--- a/重大节点进度追踪通报及存档汇总/各专业反馈标注的汇总表/污水站土建完成节点汇总_202608010（污水回复）.xlsx
+++ b/重大节点进度追踪通报及存档汇总/各专业反馈标注的汇总表/污水站土建完成节点汇总_202608010（污水回复）.xlsx
@@ -55,7 +55,7 @@
     <t>完成情况</t>
   </si>
   <si>
-    <t>责任人</t>
+    <t>乙方责任人</t>
   </si>
   <si>
     <t>4600车间</t>
@@ -4639,7 +4639,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A7:F7 A8:B8 D8:F8 A9:F9 A10:B11 D10:F11 A12:F13 A14:B14 D14:F14 A15:F19 A20:B21 D20:F21 A22:F40 A41:B41 D41:F41 A42:F45 A46:B46 D46:F46 A47:F48 A49:B49 D49:F49 A50:F134 A1:F2 A3:B3 D3:F3 A4:F5 A6:B6 D6:F6" numberStoredAsText="1"/>
+    <ignoredError sqref="D6:F6 A6:B6 A4:F5 D3:F3 A3:B3 A1:F2 A50:F134 D49:F49 A49:B49 A47:F48 D46:F46 A46:B46 A42:F45 D41:F41 A41:B41 A22:F40 D20:F21 A20:B21 A15:F19 D14:F14 A14:B14 A12:F13 D10:F11 A10:B11 A9:F9 D8:F8 A8:B8 A7:F7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>